--- a/Hardware/Other/eq -12db setting.xlsx
+++ b/Hardware/Other/eq -12db setting.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69f5ad8fb782b24f/Documents/Power Amp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69f5ad8fb782b24f/Documents/GitHub/Home-Audio-System/Hardware/Other/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{7F6360A8-71E5-4E25-AE3C-DA593094E3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/Hardware/Other/eq -12db setting.xlsx
+++ b/Hardware/Other/eq -12db setting.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{7F6360A8-71E5-4E25-AE3C-DA593094E3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{26E94E22-7D32-4E83-B796-7A64D271D4EF}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{26E94E22-7D32-4E83-B796-7A64D271D4EF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
